--- a/tests/runners/paths/config/Model_B.xlsx
+++ b/tests/runners/paths/config/Model_B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\tests\runners\paths\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laghida\Documents\Github\cassy\tests\runners\paths\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593EA98F-5796-4DED-9028-15047C014300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4904F28-5069-48C2-8DE0-90EDACCCC9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-240" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Event Fatigue" sheetId="1" r:id="rId1"/>
@@ -126,9 +126,6 @@
     <t>Is Pressure</t>
   </si>
   <si>
-    <t>Is Occasional</t>
-  </si>
-  <si>
     <t>MPa</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
   </si>
   <si>
     <t>SS316L(N)-IG_SDC-IC</t>
+  </si>
+  <si>
+    <t>Is Short Overstress</t>
   </si>
 </sst>
 </file>
@@ -614,77 +614,77 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="35.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="35.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="35.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="35.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="35.3046875" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="35.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="35.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.3046875" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I2" s="9">
         <v>30000</v>
@@ -696,30 +696,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I3" s="9">
         <v>30000</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -743,7 +743,7 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9"/>
       <c r="C5" s="11"/>
       <c r="D5" s="10"/>
@@ -755,7 +755,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -766,7 +766,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="C7" s="11"/>
       <c r="D7" s="10"/>
@@ -777,7 +777,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -788,7 +788,7 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
       <c r="C9" s="11"/>
       <c r="D9" s="10"/>
@@ -799,7 +799,7 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -810,7 +810,7 @@
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9"/>
       <c r="C11" s="11"/>
       <c r="D11" s="10"/>
@@ -821,7 +821,7 @@
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -832,7 +832,7 @@
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="C13" s="11"/>
       <c r="D13" s="10"/>
@@ -854,74 +854,74 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.69140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.84375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
         <v>51</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
         <v>52</v>
       </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>54</v>
       </c>
       <c r="I2" s="3">
         <v>35</v>
@@ -930,30 +930,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
         <v>56</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>57</v>
       </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>58</v>
-      </c>
       <c r="H3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3">
         <v>35</v>
@@ -962,30 +962,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" t="s">
         <v>52</v>
       </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>54</v>
       </c>
       <c r="I4" s="3">
         <v>35</v>
@@ -994,30 +994,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
         <v>56</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
-        <v>58</v>
-      </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="3">
         <v>35</v>
@@ -1037,21 +1037,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.53515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1080,76 +1080,76 @@
         <v>32</v>
       </c>
       <c r="J1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
       </c>
       <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -1158,30 +1158,30 @@
         <v>0.33</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
-        <v>38</v>
-      </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -1190,30 +1190,30 @@
         <v>0.33</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
         <v>37</v>
       </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1222,19 +1222,19 @@
         <v>0.33</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
       </c>
-      <c r="H6" t="s">
-        <v>38</v>
-      </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1248,14 +1248,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.69140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3046875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1332,15 +1332,15 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
-    <col min="4" max="5" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.3828125" customWidth="1"/>
+    <col min="4" max="5" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -1374,7 +1374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -1402,15 +1402,15 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1436,12 +1436,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="G4" t="s">
         <v>4</v>
       </c>
